--- a/public/downloads/cashman-project-portfolio.xlsx
+++ b/public/downloads/cashman-project-portfolio.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -511,20 +511,19 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cashman Companies — Project Portfolio (last 5 years)</t>
+          <t>Cashman Companies — Hypothetical Project Portfolio (training data)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>32 completed (or in-progress) projects across Dredging, Pile Driving, IPC Lydon, and Preload Cryogenics. Use this dataset to ask AI which project type tends to go over budget and why.</t>
+          <t>32 hypothetical projects across Dredging, Pile Driving, IPC Lydon, and Preload Cryogenics. All names, regions, and figures are made up for AI-training use only. Ask AI which project type tends to go over budget and why.</t>
         </is>
       </c>
     </row>
@@ -587,15 +586,10 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Client Satisfaction (1-5)</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -641,15 +635,12 @@
       <c r="K5" s="5" t="n">
         <v>80000</v>
       </c>
-      <c r="L5" s="6" t="n">
-        <v>5</v>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Bobby M.</t>
+        </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Bobby M.</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -695,15 +686,12 @@
       <c r="K6" s="8" t="n">
         <v>920000</v>
       </c>
-      <c r="L6" s="9" t="n">
-        <v>4</v>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Bobby M.</t>
+        </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>Bobby M.</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -749,15 +737,12 @@
       <c r="K7" s="5" t="n">
         <v>140000</v>
       </c>
-      <c r="L7" s="6" t="n">
-        <v>5</v>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Sarah K.</t>
+        </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Sarah K.</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -803,15 +788,12 @@
       <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
-        <v>5</v>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Bobby M.</t>
+        </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>Bobby M.</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -857,15 +839,12 @@
       <c r="K9" s="5" t="n">
         <v>1350000</v>
       </c>
-      <c r="L9" s="6" t="n">
-        <v>3</v>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Sarah K.</t>
+        </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Sarah K.</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -911,15 +890,12 @@
       <c r="K10" s="8" t="n">
         <v>280000</v>
       </c>
-      <c r="L10" s="9" t="n">
-        <v>5</v>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Bobby M.</t>
+        </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>Bobby M.</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -965,15 +941,12 @@
       <c r="K11" s="5" t="n">
         <v>55000</v>
       </c>
-      <c r="L11" s="6" t="n">
-        <v>4</v>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Sarah K.</t>
+        </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>Sarah K.</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1019,15 +992,12 @@
       <c r="K12" s="8" t="n">
         <v>165000</v>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>4</v>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Bobby M.</t>
+        </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>Bobby M.</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1073,15 +1043,12 @@
       <c r="K13" s="5" t="n">
         <v>145000</v>
       </c>
-      <c r="L13" s="6" t="n">
-        <v>4</v>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Mike R.</t>
+        </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>Mike R.</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1127,15 +1094,12 @@
       <c r="K14" s="8" t="n">
         <v>180000</v>
       </c>
-      <c r="L14" s="9" t="n">
-        <v>4</v>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Mike R.</t>
+        </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Mike R.</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1181,15 +1145,12 @@
       <c r="K15" s="5" t="n">
         <v>45000</v>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>5</v>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1235,15 +1196,12 @@
       <c r="K16" s="8" t="n">
         <v>60000</v>
       </c>
-      <c r="L16" s="9" t="n">
-        <v>5</v>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Mike R.</t>
+        </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>Mike R.</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1289,15 +1247,12 @@
       <c r="K17" s="5" t="n">
         <v>680000</v>
       </c>
-      <c r="L17" s="6" t="n">
-        <v>4</v>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1343,15 +1298,12 @@
       <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
-        <v>5</v>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Mike R.</t>
+        </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>Mike R.</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1397,15 +1349,12 @@
       <c r="K19" s="5" t="n">
         <v>520000</v>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>4</v>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1451,15 +1400,12 @@
       <c r="K20" s="8" t="n">
         <v>42000</v>
       </c>
-      <c r="L20" s="9" t="n">
-        <v>5</v>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Mike R.</t>
+        </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>Mike R.</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1505,15 +1451,12 @@
       <c r="K21" s="5" t="n">
         <v>860000</v>
       </c>
-      <c r="L21" s="6" t="n">
-        <v>3</v>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Peter S.</t>
+        </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Peter S.</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1559,15 +1502,12 @@
       <c r="K22" s="8" t="n">
         <v>1350000</v>
       </c>
-      <c r="L22" s="9" t="n">
-        <v>2</v>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Peter S.</t>
+        </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>Peter S.</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1613,15 +1553,12 @@
       <c r="K23" s="5" t="n">
         <v>280000</v>
       </c>
-      <c r="L23" s="6" t="n">
-        <v>4</v>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Karen H.</t>
+        </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Karen H.</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1667,15 +1604,12 @@
       <c r="K24" s="8" t="n">
         <v>75000</v>
       </c>
-      <c r="L24" s="9" t="n">
-        <v>4</v>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Karen H.</t>
+        </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>Karen H.</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1721,15 +1655,12 @@
       <c r="K25" s="5" t="n">
         <v>720000</v>
       </c>
-      <c r="L25" s="6" t="n">
-        <v>3</v>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Peter S.</t>
+        </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Peter S.</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1775,15 +1706,12 @@
       <c r="K26" s="8" t="n">
         <v>55000</v>
       </c>
-      <c r="L26" s="9" t="n">
-        <v>5</v>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Karen H.</t>
+        </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>Karen H.</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1829,15 +1757,12 @@
       <c r="K27" s="5" t="n">
         <v>1450000</v>
       </c>
-      <c r="L27" s="6" t="n">
-        <v>3</v>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Peter S.</t>
+        </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Peter S.</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1883,15 +1808,12 @@
       <c r="K28" s="8" t="n">
         <v>3900000</v>
       </c>
-      <c r="L28" s="9" t="n">
-        <v>2</v>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Peter S.</t>
+        </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>Peter S.</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1937,15 +1859,12 @@
       <c r="K29" s="5" t="n">
         <v>380000</v>
       </c>
-      <c r="L29" s="6" t="n">
-        <v>5</v>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -1991,15 +1910,12 @@
       <c r="K30" s="8" t="n">
         <v>7400000</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>2</v>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2045,15 +1961,12 @@
       <c r="K31" s="5" t="n">
         <v>12900000</v>
       </c>
-      <c r="L31" s="6" t="n">
-        <v>2</v>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Karen H.</t>
+        </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Karen H.</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2099,15 +2012,12 @@
       <c r="K32" s="8" t="n">
         <v>1500000</v>
       </c>
-      <c r="L32" s="9" t="n">
-        <v>4</v>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2153,15 +2063,12 @@
       <c r="K33" s="5" t="n">
         <v>600000</v>
       </c>
-      <c r="L33" s="6" t="n">
-        <v>5</v>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Karen H.</t>
+        </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Karen H.</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2207,15 +2114,12 @@
       <c r="K34" s="8" t="n">
         <v>3800000</v>
       </c>
-      <c r="L34" s="9" t="n">
-        <v>2</v>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2261,15 +2165,12 @@
       <c r="K35" s="5" t="n">
         <v>5500000</v>
       </c>
-      <c r="L35" s="6" t="n">
-        <v>3</v>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Karen H.</t>
+        </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>Karen H.</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
@@ -2315,15 +2216,12 @@
       <c r="K36" s="8" t="n">
         <v>15200000</v>
       </c>
-      <c r="L36" s="9" t="n">
-        <v>2</v>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Wes T.</t>
+        </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>Wes T.</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -2339,21 +2237,21 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>• Cost Variance = Final Cost − Contract Value (positive = over budget)</t>
+          <t>• All project names, regions, and figures in this workbook are HYPOTHETICAL and exist for AI-training purposes only.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>• Schedule Variance = Actual Duration − Planned Duration (positive = late)</t>
+          <t>• Cost Variance = Final Cost − Contract Value (positive = over budget)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>• Client Satisfaction is on a 1 (worst) to 5 (best) scale, captured at project closeout</t>
+          <t>• Schedule Variance = Actual Duration − Planned Duration (positive = late)</t>
         </is>
       </c>
     </row>
@@ -2364,23 +2262,15 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• All figures are hypothetical and for training only</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A40:N40"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A43:N43"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A40:M40"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A42:M42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
